--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122848538</v>
+        <v>122848834</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582796</v>
+        <v>582825</v>
       </c>
       <c r="R2" t="n">
-        <v>7041575</v>
+        <v>7041535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122848834</v>
+        <v>122848538</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582825</v>
+        <v>582796</v>
       </c>
       <c r="R3" t="n">
-        <v>7041535</v>
+        <v>7041575</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122848834</v>
+        <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582825</v>
+        <v>582796</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122848538</v>
+        <v>122848834</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582796</v>
+        <v>582825</v>
       </c>
       <c r="R3" t="n">
-        <v>7041575</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122848834</v>
+        <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582825</v>
+        <v>582796</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122848538</v>
+        <v>122848834</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582796</v>
+        <v>582825</v>
       </c>
       <c r="R3" t="n">
-        <v>7041575</v>
+        <v>7041535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2347-2025 artfynd.xlsx
+++ b/artfynd/A 2347-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122848834</v>
+        <v>122848538</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnklippen, Tjärnklippen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582825</v>
+        <v>582796</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122848538</v>
+        <v>122848577</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582796</v>
+        <v>582756</v>
       </c>
       <c r="R3" t="n">
-        <v>7041575</v>
+        <v>7041556</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,6 +886,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122848834</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärnklippen, Tjärnklippen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>582825</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7041535</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
